--- a/scraper/downloads/yad2_page_7.xlsx
+++ b/scraper/downloads/yad2_page_7.xlsx
@@ -203,7 +203,7 @@
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="9.450000000000001" customWidth="1"/>
-    <col min="3" max="3" width="14.850000000000001" customWidth="1"/>
+    <col min="3" max="3" width="17.55" customWidth="1"/>
     <col min="4" max="4" width="6.75" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
     <col min="6" max="6" width="10.8" customWidth="1"/>
@@ -333,16 +333,14 @@
       </c>
       <c t="inlineStr" r="C3">
         <is>
-          <t xml:space="preserve">שמואל הנגיד</t>
+          <t xml:space="preserve">שופט חיים כהן</t>
         </is>
       </c>
       <c r="D3" s="65">
-        <v>15</v>
-      </c>
-      <c t="inlineStr" r="E3">
-        <is>
-          <t xml:space="preserve">/50</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="E3" s="65">
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F3">
         <is>
@@ -350,16 +348,16 @@
         </is>
       </c>
       <c r="G3" s="65">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="H3">
         <is>
-          <t xml:space="preserve">57מ״ר</t>
+          <t xml:space="preserve">80מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="I3">
         <is>
-          <t xml:space="preserve">מרפסת: 4מ״ר</t>
+          <t xml:space="preserve">מרפסת: 5מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J3">
@@ -372,18 +370,8 @@
           <t xml:space="preserve">יש מחסן</t>
         </is>
       </c>
-      <c t="inlineStr" r="L3">
-        <is>
-          <t xml:space="preserve">דרום מזרח מערב</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="N3">
-        <is>
-          <t xml:space="preserve">תמר גוטליב(050) 539-0333לא לפנות</t>
-        </is>
-      </c>
       <c r="O3" s="63">
-        <v>3900000</v>
+        <v>3100000</v>
       </c>
       <c t="inlineStr" r="R3">
         <is>
@@ -392,7 +380,7 @@
       </c>
       <c t="inlineStr" r="S3">
         <is>
-          <t xml:space="preserve">אורן כהן16-01-2025</t>
+          <t xml:space="preserve">דוב רבינובץ\'31-05-2026</t>
         </is>
       </c>
     </row>
@@ -407,14 +395,16 @@
       </c>
       <c t="inlineStr" r="C4">
         <is>
-          <t xml:space="preserve">שערי חסד</t>
+          <t xml:space="preserve">שמואל הנגיד</t>
         </is>
       </c>
       <c r="D4" s="65">
-        <v>7</v>
-      </c>
-      <c r="E4" s="65">
-        <v>0</v>
+        <v>15</v>
+      </c>
+      <c t="inlineStr" r="E4">
+        <is>
+          <t xml:space="preserve">/50</t>
+        </is>
       </c>
       <c t="inlineStr" r="F4">
         <is>
@@ -422,30 +412,40 @@
         </is>
       </c>
       <c r="G4" s="65">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c t="inlineStr" r="H4">
         <is>
-          <t xml:space="preserve">153מ״ר</t>
+          <t xml:space="preserve">57מ״ר</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I4">
+        <is>
+          <t xml:space="preserve">מרפסת: 4מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J4">
         <is>
-          <t xml:space="preserve">ללא חניה</t>
+          <t xml:space="preserve">1חניות</t>
         </is>
       </c>
       <c t="inlineStr" r="K4">
         <is>
-          <t xml:space="preserve">ללא מחסן</t>
+          <t xml:space="preserve">יש מחסן</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="L4">
+        <is>
+          <t xml:space="preserve">דרום מזרח מערב</t>
         </is>
       </c>
       <c t="inlineStr" r="N4">
         <is>
-          <t xml:space="preserve">אביטבול שרלי(052) 240-8933</t>
-        </is>
-      </c>
-      <c r="O4" s="65">
-        <v>0</v>
+          <t xml:space="preserve">תמר גוטליב(050) 539-0333לא לפנות</t>
+        </is>
+      </c>
+      <c r="O4" s="63">
+        <v>3900000</v>
       </c>
       <c t="inlineStr" r="R4">
         <is>
@@ -454,7 +454,7 @@
       </c>
       <c t="inlineStr" r="S4">
         <is>
-          <t xml:space="preserve">רבקה בן זקן04-11-2024</t>
+          <t xml:space="preserve">אורן כהן16-01-2025</t>
         </is>
       </c>
     </row>
@@ -469,52 +469,114 @@
       </c>
       <c t="inlineStr" r="C5">
         <is>
+          <t xml:space="preserve">שערי חסד</t>
+        </is>
+      </c>
+      <c r="D5" s="65">
+        <v>7</v>
+      </c>
+      <c r="E5" s="65">
+        <v>0</v>
+      </c>
+      <c t="inlineStr" r="F5">
+        <is>
+          <t xml:space="preserve">דירה</t>
+        </is>
+      </c>
+      <c r="G5" s="65">
+        <v>0</v>
+      </c>
+      <c t="inlineStr" r="H5">
+        <is>
+          <t xml:space="preserve">153מ״ר</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J5">
+        <is>
+          <t xml:space="preserve">ללא חניה</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K5">
+        <is>
+          <t xml:space="preserve">ללא מחסן</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="N5">
+        <is>
+          <t xml:space="preserve">אביטבול שרלי(052) 240-8933</t>
+        </is>
+      </c>
+      <c r="O5" s="65">
+        <v>0</v>
+      </c>
+      <c t="inlineStr" r="R5">
+        <is>
+          <t xml:space="preserve">פעיל</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="S5">
+        <is>
+          <t xml:space="preserve">רבקה בן זקן04-11-2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="65">
+        <v>154</v>
+      </c>
+      <c t="inlineStr" r="B6">
+        <is>
+          <t xml:space="preserve">ירושלים</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C6">
+        <is>
           <t xml:space="preserve">שת"פ</t>
         </is>
       </c>
-      <c r="D5" s="65">
-        <v>0</v>
-      </c>
-      <c r="E5" s="65">
-        <v>0</v>
-      </c>
-      <c t="inlineStr" r="F5">
+      <c r="D6" s="65">
+        <v>0</v>
+      </c>
+      <c r="E6" s="65">
+        <v>0</v>
+      </c>
+      <c t="inlineStr" r="F6">
         <is>
           <t xml:space="preserve">דירה</t>
         </is>
       </c>
-      <c r="G5" s="65">
-        <v>0</v>
-      </c>
-      <c t="inlineStr" r="H5">
+      <c r="G6" s="65">
+        <v>0</v>
+      </c>
+      <c t="inlineStr" r="H6">
         <is>
           <t xml:space="preserve">0מ״ר</t>
         </is>
       </c>
-      <c t="inlineStr" r="J5">
+      <c t="inlineStr" r="J6">
         <is>
           <t xml:space="preserve">ללא חניה</t>
         </is>
       </c>
-      <c t="inlineStr" r="K5">
+      <c t="inlineStr" r="K6">
         <is>
           <t xml:space="preserve">ללא מחסן</t>
         </is>
       </c>
-      <c t="inlineStr" r="N5">
+      <c t="inlineStr" r="N6">
         <is>
           <t xml:space="preserve">טסט דירת שת"פ(058) 411-4686</t>
         </is>
       </c>
-      <c r="O5" s="65">
-        <v>0</v>
-      </c>
-      <c t="inlineStr" r="R5">
+      <c r="O6" s="65">
+        <v>0</v>
+      </c>
+      <c t="inlineStr" r="R6">
         <is>
           <t xml:space="preserve">פעיל</t>
         </is>
       </c>
-      <c t="inlineStr" r="S5">
+      <c t="inlineStr" r="S6">
         <is>
           <t xml:space="preserve">אין שיוך לאיש מכירות29-10-2024</t>
         </is>
